--- a/exports/PGEL_full_report.xlsx
+++ b/exports/PGEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.99</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>76.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>75.07999999999998</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-9.43</v>
+        <v>-14.52</v>
       </c>
       <c r="L2" t="n">
-        <v>13.57</v>
+        <v>15.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>1.18</v>
       </c>
       <c r="N2" t="n">
-        <v>4.62</v>
+        <v>5.56</v>
       </c>
       <c r="O2" t="n">
         <v>-1.67</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44630.38541666666</v>
+        <v>44630.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>66.7</v>
+        <v>67.7</v>
       </c>
       <c r="I3" t="n">
         <v>66.84452794589996</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>7.49</v>
+        <v>6.1</v>
       </c>
       <c r="L3" t="n">
         <v>11.93</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.2</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>76.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>73.85877454575856</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56</v>
+        <v>56.83333333333334</v>
       </c>
       <c r="K4" t="n">
-        <v>13.59</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>5.17</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.37</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44701.55208333334</v>
+        <v>44704.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>67.55</v>
+        <v>72.3</v>
       </c>
       <c r="I5" t="n">
         <v>71.44770515267879</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>8.220000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="L5" t="n">
         <v>3.26</v>
@@ -726,7 +785,7 @@
         <v>3.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>-3.25</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.99</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44796.38541666666</v>
+        <v>44796.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>89.8</v>
+        <v>88.25</v>
       </c>
       <c r="I6" t="n">
         <v>88.90304155000713</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>92</v>
+        <v>92.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>24.2</v>
+        <v>22.06</v>
       </c>
       <c r="L6" t="n">
         <v>8.85</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44816.55208333334</v>
+        <v>44817.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>90.3</v>
+        <v>95.05</v>
       </c>
       <c r="I7" t="n">
         <v>93.91590836417946</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.32</v>
+        <v>-7.71</v>
       </c>
       <c r="L7" t="n">
-        <v>7.08</v>
+        <v>7.71</v>
       </c>
       <c r="M7" t="n">
         <v>2.26</v>
       </c>
       <c r="N7" t="n">
-        <v>3.32</v>
+        <v>5.26</v>
       </c>
       <c r="O7" t="n">
         <v>-1.51</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.39</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44865.55208333334</v>
+        <v>44866.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>104.65</v>
+        <v>100.8</v>
       </c>
       <c r="I8" t="n">
         <v>103.0126278307467</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K8" t="n">
-        <v>10.1</v>
+        <v>6.05</v>
       </c>
       <c r="L8" t="n">
         <v>4.79</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44907.38541666666</v>
+        <v>44907.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>102.9</v>
+        <v>106.1</v>
       </c>
       <c r="I9" t="n">
         <v>105.6667537986149</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.08</v>
+        <v>-5.26</v>
       </c>
       <c r="L9" t="n">
         <v>7.99</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.24</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44918.38541666666</v>
+        <v>44918.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>106.65</v>
+        <v>104</v>
       </c>
       <c r="I10" t="n">
         <v>105.7595157493777</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0.52</v>
+        <v>-1.98</v>
       </c>
       <c r="L10" t="n">
         <v>3.11</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>11.34</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44932.38541666666</v>
+        <v>44932.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>112.3</v>
+        <v>115.5</v>
       </c>
       <c r="I11" t="n">
         <v>114.8455669671198</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.98</v>
+        <v>-11.06</v>
       </c>
       <c r="L11" t="n">
-        <v>10.72</v>
+        <v>11.06</v>
       </c>
       <c r="M11" t="n">
         <v>0.9399999999999999</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.91</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>119.5</v>
+        <v>107.3</v>
       </c>
       <c r="I12" t="n">
         <v>111.8920026889154</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>19</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>3.46</v>
+        <v>-7.1</v>
       </c>
       <c r="L12" t="n">
-        <v>3.38</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>0.78</v>
       </c>
       <c r="N12" t="n">
-        <v>1.69</v>
+        <v>11.3</v>
       </c>
       <c r="O12" t="n">
         <v>4.15</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>17.77</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44967.38541666666</v>
+        <v>44967.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>116.05</v>
+        <v>118.5</v>
       </c>
       <c r="I13" t="n">
         <v>117.282334297234</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.15</v>
+        <v>-10.44</v>
       </c>
       <c r="L13" t="n">
         <v>13.23</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.56</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45006.38541666666</v>
+        <v>45006.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>132.5</v>
+        <v>131.5</v>
       </c>
       <c r="I14" t="n">
         <v>132.026658025056</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K14" t="n">
-        <v>11.81</v>
+        <v>10.97</v>
       </c>
       <c r="L14" t="n">
         <v>3.08</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45022.38541666666</v>
+        <v>45022.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>139.35</v>
+        <v>141.5</v>
       </c>
       <c r="I15" t="n">
         <v>139.8733957173729</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.97</v>
+        <v>-7.6</v>
       </c>
       <c r="L15" t="n">
-        <v>6.31</v>
+        <v>8.52</v>
       </c>
       <c r="M15" t="n">
         <v>0.96</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.84</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>159.5</v>
+        <v>157.8</v>
       </c>
       <c r="I16" t="n">
         <v>158.0266044335987</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>77</v>
+        <v>77.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>12.72</v>
+        <v>11.52</v>
       </c>
       <c r="L16" t="n">
         <v>3.82</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.42</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45141.55208333334</v>
+        <v>45142.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>152.5</v>
+        <v>155.75</v>
       </c>
       <c r="I17" t="n">
         <v>155.3101892606422</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>3.36</v>
+        <v>1.3</v>
       </c>
       <c r="L17" t="n">
         <v>4.72</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.9</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45175.38541666666</v>
+        <v>45175.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>180.8</v>
+        <v>179.8</v>
       </c>
       <c r="I18" t="n">
         <v>180.3257222332897</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>16.08</v>
+        <v>15.44</v>
       </c>
       <c r="L18" t="n">
         <v>2.41</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>13.23</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45205.55208333334</v>
+        <v>45208.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>181.1</v>
+        <v>185.25</v>
       </c>
       <c r="I19" t="n">
         <v>184.8690255918591</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.72</v>
+        <v>-3.03</v>
       </c>
       <c r="L19" t="n">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="M19" t="n">
         <v>1.3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.11</v>
+        <v>3.64</v>
       </c>
       <c r="O19" t="n">
         <v>-1.56</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.66</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>203.5</v>
+        <v>191</v>
       </c>
       <c r="I20" t="n">
         <v>195.1120606550002</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K20" t="n">
-        <v>9.85</v>
+        <v>3.1</v>
       </c>
       <c r="L20" t="n">
         <v>3.27</v>
@@ -1581,7 +1820,7 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.49</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>3.64</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>16.08</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45243.38541666666</v>
+        <v>45243.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>207.1</v>
+        <v>211.7</v>
       </c>
       <c r="I21" t="n">
         <v>207.637629803829</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.43</v>
+        <v>-10.84</v>
       </c>
       <c r="L21" t="n">
-        <v>9.42</v>
+        <v>11.96</v>
       </c>
       <c r="M21" t="n">
         <v>1.66</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.7</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45293.38541666666</v>
+        <v>45293.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>229.15</v>
+        <v>228</v>
       </c>
       <c r="I22" t="n">
         <v>229.06958460517</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>49.83333333333334</v>
+        <v>50</v>
       </c>
       <c r="K22" t="n">
-        <v>8.24</v>
+        <v>7.7</v>
       </c>
       <c r="L22" t="n">
         <v>2.22</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.31</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45366.38541666666</v>
+        <v>45366.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>159.75</v>
+        <v>166.5</v>
       </c>
       <c r="I23" t="n">
         <v>165.9848514554565</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>72.83333333333333</v>
+        <v>73</v>
       </c>
       <c r="K23" t="n">
-        <v>29.93</v>
+        <v>26.97</v>
       </c>
       <c r="L23" t="n">
         <v>0.92</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>13.26</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45420.38541666666</v>
+        <v>45420.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>204</v>
+        <v>202.6</v>
       </c>
       <c r="I24" t="n">
         <v>203.092884032944</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>53.83333333333334</v>
+        <v>54</v>
       </c>
       <c r="K24" t="n">
-        <v>22.52</v>
+        <v>21.68</v>
       </c>
       <c r="L24" t="n">
         <v>7.27</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.85</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45429.55208333334</v>
+        <v>45430.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>211.5</v>
+        <v>220</v>
       </c>
       <c r="I25" t="n">
         <v>217.7488610149629</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.39</v>
+        <v>-8.59</v>
       </c>
       <c r="L25" t="n">
-        <v>7.31</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>2.45</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>273.5</v>
+        <v>248.9</v>
       </c>
       <c r="I26" t="n">
         <v>249.8475098558669</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K26" t="n">
-        <v>24.32</v>
+        <v>13.14</v>
       </c>
       <c r="L26" t="n">
         <v>2.86</v>
@@ -1923,7 +2234,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>1.86</v>
+        <v>8.99</v>
       </c>
       <c r="O26" t="n">
         <v>4.02</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>15.39</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>282.6</v>
+        <v>293.85</v>
       </c>
       <c r="I27" t="n">
         <v>284.151940315073</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>-13.54</v>
+        <v>-18.06</v>
       </c>
       <c r="L27" t="n">
-        <v>15.71</v>
+        <v>19.33</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="N27" t="n">
         <v>10.22</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>14.27</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45491.38541666666</v>
+        <v>45491.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>360.55</v>
+        <v>356.5</v>
       </c>
       <c r="I28" t="n">
         <v>357.0031254859855</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>22.7</v>
+        <v>21.32</v>
       </c>
       <c r="L28" t="n">
         <v>3.11</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.71</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45496.55208333334</v>
+        <v>45497.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>375</v>
+        <v>401.05</v>
       </c>
       <c r="I29" t="n">
         <v>394.3255403552098</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.19</v>
+        <v>-12.5</v>
       </c>
       <c r="L29" t="n">
-        <v>7.12</v>
+        <v>14.43</v>
       </c>
       <c r="M29" t="n">
-        <v>0.43</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>6.52</v>
+        <v>6.85</v>
       </c>
       <c r="O29" t="n">
         <v>-2.14</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.89</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45531.38541666666</v>
+        <v>45531.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>509.1</v>
+        <v>504.1</v>
       </c>
       <c r="I30" t="n">
         <v>507.1005456219322</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>26.94</v>
+        <v>25.7</v>
       </c>
       <c r="L30" t="n">
         <v>4.1</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>13.59</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="I31" t="n">
         <v>548.0181892547843</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.92</v>
+        <v>-10.1</v>
       </c>
       <c r="L31" t="n">
-        <v>8.390000000000001</v>
+        <v>12.08</v>
       </c>
       <c r="M31" t="n">
         <v>1.32</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>12.23</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>630</v>
+        <v>604.85</v>
       </c>
       <c r="I32" t="n">
         <v>618.9914669247152</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K32" t="n">
-        <v>13.51</v>
+        <v>8.98</v>
       </c>
       <c r="L32" t="n">
         <v>4.07</v>
       </c>
       <c r="M32" t="n">
-        <v>0.87</v>
+        <v>2.06</v>
       </c>
       <c r="N32" t="n">
         <v>3.61</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45574.38541666666</v>
+        <v>45574.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>618.1</v>
+        <v>620</v>
       </c>
       <c r="I33" t="n">
         <v>619.2366218854186</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.19</v>
+        <v>-2.5</v>
       </c>
       <c r="L33" t="n">
         <v>5.3</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.64</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45666.38541666666</v>
+        <v>45666.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>927.95</v>
+        <v>921.75</v>
       </c>
       <c r="I34" t="n">
         <v>924.5581477464185</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>91.83333333333333</v>
+        <v>92</v>
       </c>
       <c r="K34" t="n">
-        <v>49.67</v>
+        <v>48.67</v>
       </c>
       <c r="L34" t="n">
         <v>11.78</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>10.93</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45691.55208333334</v>
+        <v>45692.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>782.8</v>
+        <v>805.4</v>
       </c>
       <c r="I35" t="n">
         <v>796.7601727027869</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>15.07</v>
+        <v>12.62</v>
       </c>
       <c r="L35" t="n">
         <v>1.21</v>
       </c>
       <c r="M35" t="n">
-        <v>2.05</v>
+        <v>4.62</v>
       </c>
       <c r="N35" t="n">
         <v>14.82</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>16.26</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>812.75</v>
+        <v>764.65</v>
       </c>
       <c r="I36" t="n">
         <v>771.8567887435702</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>0.91</v>
+        <v>-5.06</v>
       </c>
       <c r="L36" t="n">
-        <v>5.11</v>
+        <v>5.56</v>
       </c>
       <c r="M36" t="n">
         <v>1.22</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>18.87</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>838.3</v>
+        <v>861.85</v>
       </c>
       <c r="I37" t="n">
         <v>852.5140701177567</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.630000000000001</v>
+        <v>-12.71</v>
       </c>
       <c r="L37" t="n">
-        <v>10.7</v>
+        <v>14.99</v>
       </c>
       <c r="M37" t="n">
         <v>2.44</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>12.24</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>878</v>
+        <v>788.65</v>
       </c>
       <c r="I38" t="n">
         <v>864.867121730671</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K38" t="n">
-        <v>1.87</v>
+        <v>-8.49</v>
       </c>
       <c r="L38" t="n">
-        <v>5.42</v>
+        <v>17.07</v>
       </c>
       <c r="M38" t="n">
-        <v>1.96</v>
+        <v>18.6</v>
       </c>
       <c r="N38" t="n">
-        <v>6.7</v>
+        <v>7.06</v>
       </c>
       <c r="O38" t="n">
         <v>1.39</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>19.18</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>920</v>
+        <v>961.15</v>
       </c>
       <c r="I39" t="n">
         <v>939.8983089904012</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-16.66</v>
+        <v>-21.87</v>
       </c>
       <c r="L39" t="n">
-        <v>17.04</v>
+        <v>23.63</v>
       </c>
       <c r="M39" t="n">
         <v>4.23</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>14.77</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45772.38541666666</v>
+        <v>45772.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>880.85</v>
+        <v>870.8</v>
       </c>
       <c r="I40" t="n">
         <v>876.6767229545793</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.35</v>
+        <v>-9.4</v>
       </c>
       <c r="L40" t="n">
         <v>10.67</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.02</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>738.85</v>
+        <v>778.5</v>
       </c>
       <c r="I41" t="n">
         <v>775.8185309681553</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>74</v>
+        <v>74.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>15.15</v>
+        <v>10.6</v>
       </c>
       <c r="L41" t="n">
         <v>5.27</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.77</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>788</v>
+        <v>761.3</v>
       </c>
       <c r="I42" t="n">
         <v>777.8665029350882</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>1.22</v>
+        <v>-2.21</v>
       </c>
       <c r="L42" t="n">
         <v>4.95</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.08</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45938.55208333334</v>
+        <v>45939.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>514.8</v>
+        <v>546.55</v>
       </c>
       <c r="I43" t="n">
         <v>538.7151976240971</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K43" t="n">
-        <v>32.38</v>
+        <v>28.21</v>
       </c>
       <c r="L43" t="n">
         <v>3.94</v>
@@ -2892,7 +3407,7 @@
         <v>6.54</v>
       </c>
       <c r="N43" t="n">
-        <v>8.029999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O43" t="n">
         <v>-4.61</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45967.55208333334</v>
+        <v>45968.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>551</v>
+        <v>525.75</v>
       </c>
       <c r="I44" t="n">
         <v>550.9131165270927</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8100000000000001</v>
+        <v>-3.81</v>
       </c>
       <c r="L44" t="n">
         <v>5.83</v>
       </c>
       <c r="M44" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="N44" t="n">
-        <v>3.43</v>
+        <v>3.81</v>
       </c>
       <c r="O44" t="n">
         <v>8.109999999999999</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>7.69</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45973.55208333334</v>
+        <v>45974.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>527.75</v>
+        <v>566.75</v>
       </c>
       <c r="I45" t="n">
         <v>560.9562654561342</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.38</v>
+        <v>-7.8</v>
       </c>
       <c r="L45" t="n">
-        <v>3.09</v>
+        <v>8.02</v>
       </c>
       <c r="M45" t="n">
-        <v>0.19</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>0.74</v>
+        <v>6.21</v>
       </c>
       <c r="O45" t="n">
         <v>-3.81</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.75</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45996.38541666666</v>
+        <v>45996.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>567</v>
+        <v>553.8</v>
       </c>
       <c r="I46" t="n">
         <v>556.2927558996622</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>0.04</v>
+        <v>-2.28</v>
       </c>
       <c r="L46" t="n">
         <v>6.84</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.8</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>566.85</v>
+        <v>571.95</v>
       </c>
       <c r="I47" t="n">
         <v>570.8707603884278</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.36</v>
+        <v>-3.28</v>
       </c>
       <c r="L47" t="n">
         <v>4.19</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.62</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46038.38541666666</v>
+        <v>46038.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>587.4</v>
+        <v>585.3</v>
       </c>
       <c r="I48" t="n">
         <v>585.8020451415869</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="L48" t="n">
         <v>2.15</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.53</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46055.38541666666</v>
+        <v>46055.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>553.6</v>
+        <v>563.55</v>
       </c>
       <c r="I49" t="n">
         <v>563.1009039652876</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K49" t="n">
-        <v>5.42</v>
+        <v>3.72</v>
       </c>
       <c r="L49" t="n">
         <v>0.5</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.34</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>618</v>
+        <v>584.8</v>
       </c>
       <c r="I50" t="n">
         <v>590.3744472247253</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>28</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>9.66</v>
+        <v>3.77</v>
       </c>
       <c r="L50" t="n">
         <v>3.56</v>
@@ -3291,7 +3890,7 @@
         <v>5.17</v>
       </c>
       <c r="N50" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O50" t="n">
         <v>3.98</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.32</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46125.55208333334</v>
+        <v>46127.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>488.8</v>
+        <v>531.8</v>
       </c>
       <c r="I51" t="n">
         <v>492.7050863442813</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>16.42</v>
+        <v>9.06</v>
       </c>
       <c r="L51" t="n">
         <v>6.15</v>
@@ -3348,7 +3959,7 @@
         <v>7.12</v>
       </c>
       <c r="N51" t="n">
-        <v>9.94</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="O51" t="n">
         <v>-4.1</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>14.74</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>551</v>
+        <v>521.35</v>
       </c>
       <c r="I52" t="n">
         <v>528.2776400074101</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K52" t="n">
-        <v>3.61</v>
+        <v>-1.97</v>
       </c>
       <c r="L52" t="n">
         <v>6.97</v>
       </c>
       <c r="M52" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="N52" t="n">
         <v>3.52</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.71</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46188.55208333334</v>
+        <v>46189.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>491.45</v>
+        <v>525.2</v>
       </c>
       <c r="I53" t="n">
         <v>496.0347831733909</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K53" t="n">
-        <v>5.74</v>
+        <v>-0.74</v>
       </c>
       <c r="L53" t="n">
         <v>5.45</v>
@@ -3462,7 +4097,7 @@
         <v>2.77</v>
       </c>
       <c r="N53" t="n">
-        <v>4.98</v>
+        <v>7.36</v>
       </c>
       <c r="O53" t="n">
         <v>-2.81</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.85</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46224.55208333334</v>
+        <v>46225.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>609</v>
+        <v>573.95</v>
       </c>
       <c r="I54" t="n">
         <v>574.1586857090563</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>15.96</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L54" t="n">
         <v>6.42</v>
@@ -3519,7 +4166,7 @@
         <v>1.11</v>
       </c>
       <c r="N54" t="n">
-        <v>2.84</v>
+        <v>5.58</v>
       </c>
       <c r="O54" t="n">
         <v>7.36</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>11.1</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46233.38541666666</v>
+        <v>46233.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="I55" t="n">
         <v>612.2689154947841</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.46</v>
+        <v>-7.15</v>
       </c>
       <c r="L55" t="n">
         <v>8.49</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.8</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>584.5</v>
+        <v>578.45</v>
       </c>
       <c r="I56" t="n">
         <v>581.5043268254449</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.96</v>
+        <v>-5.94</v>
       </c>
       <c r="L56" t="n">
-        <v>5.02</v>
+        <v>7.09</v>
       </c>
       <c r="M56" t="n">
         <v>0.38</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.01</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>486.5</v>
+        <v>525.65</v>
       </c>
       <c r="I57" t="n">
         <v>511.3729564094948</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K57" t="n">
-        <v>15.9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L57" t="n">
         <v>1.23</v>
@@ -3690,7 +4373,7 @@
         <v>1.51</v>
       </c>
       <c r="N57" t="n">
-        <v>1.91</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="O57" t="n">
         <v>-1.86</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>11.73</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>508.15</v>
+        <v>493</v>
       </c>
       <c r="I58" t="n">
         <v>494.7962993743358</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.33</v>
+        <v>-6.21</v>
       </c>
       <c r="L58" t="n">
         <v>8.02</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.94</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>475</v>
+        <v>507.45</v>
       </c>
       <c r="I59" t="n">
         <v>503.0543407109794</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>3.65</v>
+        <v>-2.93</v>
       </c>
       <c r="L59" t="n">
         <v>4.41</v>
       </c>
       <c r="M59" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9</v>
+        <v>4.92</v>
       </c>
       <c r="O59" t="n">
         <v>-2.98</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3864,6 +4583,12 @@
       <c r="Q60" t="n">
         <v>2</v>
       </c>
+      <c r="R60" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5966,7 +6691,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.2</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="6">
@@ -5976,7 +6701,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.1</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="7">
@@ -5986,7 +6711,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="8">
@@ -5996,7 +6721,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="9">
@@ -6006,7 +6731,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39.8</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="10">
@@ -6016,7 +6741,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -6026,7 +6751,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -6036,7 +6761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -6046,7 +6771,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.1</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="14">
@@ -6056,7 +6781,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.8</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="15">
@@ -6066,7 +6791,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.69</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="16">
@@ -6076,7 +6801,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.91</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="17">
@@ -6086,7 +6811,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49.67</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="18">
@@ -6096,7 +6821,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="19">
@@ -6106,7 +6831,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.08</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="20">
@@ -6116,7 +6841,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.22</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="21">
@@ -6126,7 +6851,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.04</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="22">
@@ -6136,7 +6861,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -6146,7 +6871,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -6156,7 +6881,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.11</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="25">
@@ -6166,7 +6891,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.66</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="26">
@@ -6176,7 +6901,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -6196,7 +6921,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
